--- a/pedidos/F2026021S.xlsx
+++ b/pedidos/F2026021S.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/pedidos/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_75E143F8650B4B26B12D4CD75DE93C41787CA5F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC7DFF0-BC07-43EC-B612-64CC857628A8}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="1275" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1570,8 +1576,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1634,13 +1640,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1678,7 +1692,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1712,6 +1726,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1746,9 +1761,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1921,11 +1937,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI297"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2110,15 +2188,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-54.08938262858074</v>
+        <v>-54.089382628580744</v>
       </c>
       <c r="C2">
-        <v>-21.41989900408038</v>
+        <v>-21.419899004080381</v>
       </c>
       <c r="D2" t="s">
         <v>61</v>
@@ -2190,15 +2268,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:61">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-54.08938262858074</v>
+        <v>-54.089382628580744</v>
       </c>
       <c r="C3">
-        <v>-21.41989900408038</v>
+        <v>-21.419899004080381</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -2270,15 +2348,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="4" spans="1:61">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>-54.08773750888297</v>
+        <v>-54.087737508882967</v>
       </c>
       <c r="C4">
-        <v>-21.4228378045286</v>
+        <v>-21.422837804528601</v>
       </c>
       <c r="D4" t="s">
         <v>62</v>
@@ -2350,15 +2428,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>-54.08773750888297</v>
+        <v>-54.087737508882967</v>
       </c>
       <c r="C5">
-        <v>-21.4228378045286</v>
+        <v>-21.422837804528601</v>
       </c>
       <c r="D5" t="s">
         <v>62</v>
@@ -2427,15 +2505,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6">
-        <v>-54.08452032356069</v>
+        <v>-54.084520323560689</v>
       </c>
       <c r="C6">
-        <v>-21.425543555302</v>
+        <v>-21.425543555301999</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
@@ -2504,15 +2582,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:61">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7">
-        <v>-54.08452032356069</v>
+        <v>-54.084520323560689</v>
       </c>
       <c r="C7">
-        <v>-21.425543555302</v>
+        <v>-21.425543555301999</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -2581,15 +2659,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8">
-        <v>-54.17362920000001</v>
+        <v>-54.173629200000008</v>
       </c>
       <c r="C8">
-        <v>-21.45194038999995</v>
+        <v>-21.451940389999951</v>
       </c>
       <c r="D8" t="s">
         <v>64</v>
@@ -2661,15 +2739,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
       <c r="B9">
-        <v>-54.17362920000001</v>
+        <v>-54.173629200000008</v>
       </c>
       <c r="C9">
-        <v>-21.45194038999995</v>
+        <v>-21.451940389999951</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -2741,15 +2819,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10">
-        <v>-54.17355295000001</v>
+        <v>-54.173552950000008</v>
       </c>
       <c r="C10">
-        <v>-21.45460190999996</v>
+        <v>-21.454601909999958</v>
       </c>
       <c r="D10" t="s">
         <v>65</v>
@@ -2821,15 +2899,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:61">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11">
-        <v>-54.17355295000001</v>
+        <v>-54.173552950000008</v>
       </c>
       <c r="C11">
-        <v>-21.45460190999996</v>
+        <v>-21.454601909999958</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -2898,15 +2976,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:61">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6</v>
       </c>
       <c r="B12">
-        <v>-54.17622033000001</v>
+        <v>-54.176220330000007</v>
       </c>
       <c r="C12">
-        <v>-21.45798140000002</v>
+        <v>-21.457981400000019</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
@@ -2975,15 +3053,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:61">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
       <c r="B13">
-        <v>-54.17622033000001</v>
+        <v>-54.176220330000007</v>
       </c>
       <c r="C13">
-        <v>-21.45798140000002</v>
+        <v>-21.457981400000019</v>
       </c>
       <c r="D13" t="s">
         <v>66</v>
@@ -3052,15 +3130,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:61">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
       <c r="B14">
-        <v>-54.17138237000002</v>
+        <v>-54.171382370000018</v>
       </c>
       <c r="C14">
-        <v>-21.45778791999997</v>
+        <v>-21.457787919999969</v>
       </c>
       <c r="D14" t="s">
         <v>67</v>
@@ -3129,15 +3207,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:61">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-54.17138237000002</v>
+        <v>-54.171382370000018</v>
       </c>
       <c r="C15">
-        <v>-21.45778791999997</v>
+        <v>-21.457787919999969</v>
       </c>
       <c r="D15" t="s">
         <v>67</v>
@@ -3206,12 +3284,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:61">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>8</v>
       </c>
       <c r="B16">
-        <v>-54.16714837000001</v>
+        <v>-54.167148370000007</v>
       </c>
       <c r="C16">
         <v>-21.45750882999997</v>
@@ -3283,12 +3361,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>8</v>
       </c>
       <c r="B17">
-        <v>-54.16714837000001</v>
+        <v>-54.167148370000007</v>
       </c>
       <c r="C17">
         <v>-21.45750882999997</v>
@@ -3360,7 +3438,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9</v>
       </c>
@@ -3368,7 +3446,7 @@
         <v>-54.16785921000001</v>
       </c>
       <c r="C18">
-        <v>-21.46271761000003</v>
+        <v>-21.462717610000031</v>
       </c>
       <c r="D18" t="s">
         <v>69</v>
@@ -3440,7 +3518,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9</v>
       </c>
@@ -3448,7 +3526,7 @@
         <v>-54.16785921000001</v>
       </c>
       <c r="C19">
-        <v>-21.46271761000003</v>
+        <v>-21.462717610000031</v>
       </c>
       <c r="D19" t="s">
         <v>69</v>
@@ -3517,15 +3595,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>10</v>
       </c>
       <c r="B20">
-        <v>-54.16223196000001</v>
+        <v>-54.162231960000007</v>
       </c>
       <c r="C20">
-        <v>-21.46017962999999</v>
+        <v>-21.460179629999988</v>
       </c>
       <c r="D20" t="s">
         <v>70</v>
@@ -3597,15 +3675,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10</v>
       </c>
       <c r="B21">
-        <v>-54.16223196000001</v>
+        <v>-54.162231960000007</v>
       </c>
       <c r="C21">
-        <v>-21.46017962999999</v>
+        <v>-21.460179629999988</v>
       </c>
       <c r="D21" t="s">
         <v>70</v>
@@ -3674,12 +3752,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>11</v>
       </c>
       <c r="B22">
-        <v>-54.16319755999999</v>
+        <v>-54.163197559999993</v>
       </c>
       <c r="C22">
         <v>-21.46419923999996</v>
@@ -3751,12 +3829,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>11</v>
       </c>
       <c r="B23">
-        <v>-54.16319755999999</v>
+        <v>-54.163197559999993</v>
       </c>
       <c r="C23">
         <v>-21.46419923999996</v>
@@ -3828,15 +3906,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>12</v>
       </c>
       <c r="B24">
-        <v>-54.15878783999997</v>
+        <v>-54.158787839999967</v>
       </c>
       <c r="C24">
-        <v>-21.46400207999997</v>
+        <v>-21.464002079999968</v>
       </c>
       <c r="D24" t="s">
         <v>72</v>
@@ -3905,15 +3983,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12</v>
       </c>
       <c r="B25">
-        <v>-54.15878783999997</v>
+        <v>-54.158787839999967</v>
       </c>
       <c r="C25">
-        <v>-21.46400207999997</v>
+        <v>-21.464002079999968</v>
       </c>
       <c r="D25" t="s">
         <v>72</v>
@@ -3982,12 +4060,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>13</v>
       </c>
       <c r="B26">
-        <v>-54.16078498</v>
+        <v>-54.160784980000003</v>
       </c>
       <c r="C26">
         <v>-21.46848097999996</v>
@@ -4062,12 +4140,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>13</v>
       </c>
       <c r="B27">
-        <v>-54.16078498</v>
+        <v>-54.160784980000003</v>
       </c>
       <c r="C27">
         <v>-21.46848097999996</v>
@@ -4139,7 +4217,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>14</v>
       </c>
@@ -4147,7 +4225,7 @@
         <v>-54.26530017000001</v>
       </c>
       <c r="C28">
-        <v>-21.56036541999998</v>
+        <v>-21.560365419999979</v>
       </c>
       <c r="D28" t="s">
         <v>74</v>
@@ -4219,7 +4297,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14</v>
       </c>
@@ -4227,7 +4305,7 @@
         <v>-54.26530017000001</v>
       </c>
       <c r="C29">
-        <v>-21.56036541999998</v>
+        <v>-21.560365419999979</v>
       </c>
       <c r="D29" t="s">
         <v>74</v>
@@ -4299,7 +4377,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>15</v>
       </c>
@@ -4307,7 +4385,7 @@
         <v>-54.28626152999999</v>
       </c>
       <c r="C30">
-        <v>-21.57166435999999</v>
+        <v>-21.571664359999989</v>
       </c>
       <c r="D30" t="s">
         <v>75</v>
@@ -4379,7 +4457,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>15</v>
       </c>
@@ -4387,7 +4465,7 @@
         <v>-54.28626152999999</v>
       </c>
       <c r="C31">
-        <v>-21.57166435999999</v>
+        <v>-21.571664359999989</v>
       </c>
       <c r="D31" t="s">
         <v>75</v>
@@ -4456,15 +4534,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>16</v>
       </c>
       <c r="B32">
-        <v>-54.28141362</v>
+        <v>-54.281413620000002</v>
       </c>
       <c r="C32">
-        <v>-21.57243333999997</v>
+        <v>-21.572433339999971</v>
       </c>
       <c r="D32" t="s">
         <v>76</v>
@@ -4533,15 +4611,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>16</v>
       </c>
       <c r="B33">
-        <v>-54.28141362</v>
+        <v>-54.281413620000002</v>
       </c>
       <c r="C33">
-        <v>-21.57243333999997</v>
+        <v>-21.572433339999971</v>
       </c>
       <c r="D33" t="s">
         <v>76</v>
@@ -4610,15 +4688,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>17</v>
       </c>
       <c r="B34">
-        <v>-54.26733097000002</v>
+        <v>-54.267330970000017</v>
       </c>
       <c r="C34">
-        <v>-21.65814491</v>
+        <v>-21.658144910000001</v>
       </c>
       <c r="D34" t="s">
         <v>77</v>
@@ -4690,15 +4768,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>17</v>
       </c>
       <c r="B35">
-        <v>-54.26733097000002</v>
+        <v>-54.267330970000017</v>
       </c>
       <c r="C35">
-        <v>-21.65814491</v>
+        <v>-21.658144910000001</v>
       </c>
       <c r="D35" t="s">
         <v>77</v>
@@ -4770,15 +4848,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>18</v>
       </c>
       <c r="B36">
-        <v>-54.2021242782177</v>
+        <v>-54.202124278217703</v>
       </c>
       <c r="C36">
-        <v>-21.51237320409187</v>
+        <v>-21.512373204091869</v>
       </c>
       <c r="D36" t="s">
         <v>78</v>
@@ -4850,15 +4928,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>18</v>
       </c>
       <c r="B37">
-        <v>-54.2021242782177</v>
+        <v>-54.202124278217703</v>
       </c>
       <c r="C37">
-        <v>-21.51237320409187</v>
+        <v>-21.512373204091869</v>
       </c>
       <c r="D37" t="s">
         <v>78</v>
@@ -4930,15 +5008,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>19</v>
       </c>
       <c r="B38">
-        <v>-54.29000370682406</v>
+        <v>-54.290003706824059</v>
       </c>
       <c r="C38">
-        <v>-21.53361160971196</v>
+        <v>-21.533611609711961</v>
       </c>
       <c r="D38" t="s">
         <v>79</v>
@@ -5010,15 +5088,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>19</v>
       </c>
       <c r="B39">
-        <v>-54.29000370682406</v>
+        <v>-54.290003706824059</v>
       </c>
       <c r="C39">
-        <v>-21.53361160971196</v>
+        <v>-21.533611609711961</v>
       </c>
       <c r="D39" t="s">
         <v>79</v>
@@ -5090,15 +5168,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>20</v>
       </c>
       <c r="B40">
-        <v>-54.2595037566323</v>
+        <v>-54.259503756632299</v>
       </c>
       <c r="C40">
-        <v>-21.58471849657576</v>
+        <v>-21.584718496575761</v>
       </c>
       <c r="D40" t="s">
         <v>80</v>
@@ -5170,15 +5248,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20</v>
       </c>
       <c r="B41">
-        <v>-54.2595037566323</v>
+        <v>-54.259503756632299</v>
       </c>
       <c r="C41">
-        <v>-21.58471849657576</v>
+        <v>-21.584718496575761</v>
       </c>
       <c r="D41" t="s">
         <v>80</v>
@@ -5250,15 +5328,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>21</v>
       </c>
       <c r="B42">
-        <v>-54.26152445726617</v>
+        <v>-54.261524457266169</v>
       </c>
       <c r="C42">
-        <v>-21.58791793924594</v>
+        <v>-21.587917939245941</v>
       </c>
       <c r="D42" t="s">
         <v>81</v>
@@ -5330,15 +5408,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>21</v>
       </c>
       <c r="B43">
-        <v>-54.26152445726617</v>
+        <v>-54.261524457266169</v>
       </c>
       <c r="C43">
-        <v>-21.58791793924594</v>
+        <v>-21.587917939245941</v>
       </c>
       <c r="D43" t="s">
         <v>81</v>
@@ -5407,7 +5485,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>22</v>
       </c>
@@ -5415,7 +5493,7 @@
         <v>-54.07402027761924</v>
       </c>
       <c r="C44">
-        <v>-21.59934752720605</v>
+        <v>-21.599347527206049</v>
       </c>
       <c r="D44" t="s">
         <v>82</v>
@@ -5487,7 +5565,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>22</v>
       </c>
@@ -5495,7 +5573,7 @@
         <v>-54.07402027761924</v>
       </c>
       <c r="C45">
-        <v>-21.59934752720605</v>
+        <v>-21.599347527206049</v>
       </c>
       <c r="D45" t="s">
         <v>82</v>
@@ -5567,15 +5645,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>23</v>
       </c>
       <c r="B46">
-        <v>-54.07082083494901</v>
+        <v>-54.070820834949011</v>
       </c>
       <c r="C46">
-        <v>-21.60094724854117</v>
+        <v>-21.600947248541171</v>
       </c>
       <c r="D46" t="s">
         <v>83</v>
@@ -5647,15 +5725,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>23</v>
       </c>
       <c r="B47">
-        <v>-54.07082083494901</v>
+        <v>-54.070820834949011</v>
       </c>
       <c r="C47">
-        <v>-21.60094724854117</v>
+        <v>-21.600947248541171</v>
       </c>
       <c r="D47" t="s">
         <v>83</v>
@@ -5724,15 +5802,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>24</v>
       </c>
       <c r="B48">
-        <v>-54.0719153811257</v>
+        <v>-54.071915381125699</v>
       </c>
       <c r="C48">
-        <v>-21.60498864980877</v>
+        <v>-21.604988649808771</v>
       </c>
       <c r="D48" t="s">
         <v>84</v>
@@ -5801,15 +5879,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="49" spans="1:35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>24</v>
       </c>
       <c r="B49">
-        <v>-54.0719153811257</v>
+        <v>-54.071915381125699</v>
       </c>
       <c r="C49">
-        <v>-21.60498864980877</v>
+        <v>-21.604988649808771</v>
       </c>
       <c r="D49" t="s">
         <v>84</v>
@@ -5878,15 +5956,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="50" spans="1:35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>25</v>
       </c>
       <c r="B50">
-        <v>-54.19951411258366</v>
+        <v>-54.199514112583657</v>
       </c>
       <c r="C50">
-        <v>-21.45514036831196</v>
+        <v>-21.455140368311959</v>
       </c>
       <c r="D50" t="s">
         <v>85</v>
@@ -5958,15 +6036,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="51" spans="1:35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>25</v>
       </c>
       <c r="B51">
-        <v>-54.19951411258366</v>
+        <v>-54.199514112583657</v>
       </c>
       <c r="C51">
-        <v>-21.45514036831196</v>
+        <v>-21.455140368311959</v>
       </c>
       <c r="D51" t="s">
         <v>85</v>
@@ -6038,15 +6116,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="52" spans="1:35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>26</v>
       </c>
       <c r="B52">
-        <v>-54.19817413069315</v>
+        <v>-54.198174130693147</v>
       </c>
       <c r="C52">
-        <v>-21.45932175758479</v>
+        <v>-21.459321757584789</v>
       </c>
       <c r="D52" t="s">
         <v>86</v>
@@ -6118,15 +6196,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="53" spans="1:35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>26</v>
       </c>
       <c r="B53">
-        <v>-54.19817413069315</v>
+        <v>-54.198174130693147</v>
       </c>
       <c r="C53">
-        <v>-21.45932175758479</v>
+        <v>-21.459321757584789</v>
       </c>
       <c r="D53" t="s">
         <v>86</v>
@@ -6195,15 +6273,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="54" spans="1:35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>27</v>
       </c>
       <c r="B54">
-        <v>-54.13643955196284</v>
+        <v>-54.136439551962837</v>
       </c>
       <c r="C54">
-        <v>-21.44305625265526</v>
+        <v>-21.443056252655261</v>
       </c>
       <c r="D54" t="s">
         <v>87</v>
@@ -6275,15 +6353,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="55" spans="1:35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>27</v>
       </c>
       <c r="B55">
-        <v>-54.13643955196284</v>
+        <v>-54.136439551962837</v>
       </c>
       <c r="C55">
-        <v>-21.44305625265526</v>
+        <v>-21.443056252655261</v>
       </c>
       <c r="D55" t="s">
         <v>87</v>
@@ -6355,15 +6433,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="56" spans="1:35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1</v>
       </c>
       <c r="B56">
-        <v>-54.03062838189808</v>
+        <v>-54.030628381898083</v>
       </c>
       <c r="C56">
-        <v>-21.80137496899905</v>
+        <v>-21.801374968999049</v>
       </c>
       <c r="D56" t="s">
         <v>88</v>
@@ -6435,15 +6513,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="57" spans="1:35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1</v>
       </c>
       <c r="B57">
-        <v>-54.03062838189808</v>
+        <v>-54.030628381898083</v>
       </c>
       <c r="C57">
-        <v>-21.80137496899905</v>
+        <v>-21.801374968999049</v>
       </c>
       <c r="D57" t="s">
         <v>88</v>
@@ -6515,15 +6593,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="58" spans="1:35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2</v>
       </c>
       <c r="B58">
-        <v>-54.03092554792921</v>
+        <v>-54.030925547929208</v>
       </c>
       <c r="C58">
-        <v>-21.80516019141998</v>
+        <v>-21.805160191419979</v>
       </c>
       <c r="D58" t="s">
         <v>89</v>
@@ -6595,15 +6673,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="59" spans="1:35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2</v>
       </c>
       <c r="B59">
-        <v>-54.03092554792921</v>
+        <v>-54.030925547929208</v>
       </c>
       <c r="C59">
-        <v>-21.80516019141998</v>
+        <v>-21.805160191419979</v>
       </c>
       <c r="D59" t="s">
         <v>89</v>
@@ -6672,15 +6750,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="60" spans="1:35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>3</v>
       </c>
       <c r="B60">
-        <v>-54.02515587005148</v>
+        <v>-54.025155870051478</v>
       </c>
       <c r="C60">
-        <v>-21.80425069868181</v>
+        <v>-21.804250698681809</v>
       </c>
       <c r="D60" t="s">
         <v>90</v>
@@ -6749,15 +6827,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="61" spans="1:35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3</v>
       </c>
       <c r="B61">
-        <v>-54.02515587005148</v>
+        <v>-54.025155870051478</v>
       </c>
       <c r="C61">
-        <v>-21.80425069868181</v>
+        <v>-21.804250698681809</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -6826,15 +6904,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="62" spans="1:35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>4</v>
       </c>
       <c r="B62">
-        <v>-54.02196560053444</v>
+        <v>-54.021965600534443</v>
       </c>
       <c r="C62">
-        <v>-21.80765985957441</v>
+        <v>-21.807659859574411</v>
       </c>
       <c r="D62" t="s">
         <v>91</v>
@@ -6903,15 +6981,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="63" spans="1:35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>4</v>
       </c>
       <c r="B63">
-        <v>-54.02196560053444</v>
+        <v>-54.021965600534443</v>
       </c>
       <c r="C63">
-        <v>-21.80765985957441</v>
+        <v>-21.807659859574411</v>
       </c>
       <c r="D63" t="s">
         <v>91</v>
@@ -6980,15 +7058,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>5</v>
       </c>
       <c r="B64">
-        <v>-54.13092143000001</v>
+        <v>-54.130921430000008</v>
       </c>
       <c r="C64">
-        <v>-21.83743706</v>
+        <v>-21.837437059999999</v>
       </c>
       <c r="D64" t="s">
         <v>92</v>
@@ -7060,15 +7138,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="65" spans="1:35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>5</v>
       </c>
       <c r="B65">
-        <v>-54.13092143000001</v>
+        <v>-54.130921430000008</v>
       </c>
       <c r="C65">
-        <v>-21.83743706</v>
+        <v>-21.837437059999999</v>
       </c>
       <c r="D65" t="s">
         <v>92</v>
@@ -7140,15 +7218,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="66" spans="1:35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>6</v>
       </c>
       <c r="B66">
-        <v>-54.12718268</v>
+        <v>-54.127182679999997</v>
       </c>
       <c r="C66">
-        <v>-21.83947428999998</v>
+        <v>-21.839474289999981</v>
       </c>
       <c r="D66" t="s">
         <v>93</v>
@@ -7220,15 +7298,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6</v>
       </c>
       <c r="B67">
-        <v>-54.12718268</v>
+        <v>-54.127182679999997</v>
       </c>
       <c r="C67">
-        <v>-21.83947428999998</v>
+        <v>-21.839474289999981</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
@@ -7297,15 +7375,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="68" spans="1:35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7</v>
       </c>
       <c r="B68">
-        <v>-54.12374971000001</v>
+        <v>-54.123749710000013</v>
       </c>
       <c r="C68">
-        <v>-21.83942259</v>
+        <v>-21.839422590000002</v>
       </c>
       <c r="D68" t="s">
         <v>94</v>
@@ -7374,15 +7452,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="69" spans="1:35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>7</v>
       </c>
       <c r="B69">
-        <v>-54.12374971000001</v>
+        <v>-54.123749710000013</v>
       </c>
       <c r="C69">
-        <v>-21.83942259</v>
+        <v>-21.839422590000002</v>
       </c>
       <c r="D69" t="s">
         <v>94</v>
@@ -7451,15 +7529,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="70" spans="1:35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>8</v>
       </c>
       <c r="B70">
-        <v>-54.07309610000001</v>
+        <v>-54.073096100000008</v>
       </c>
       <c r="C70">
-        <v>-21.78910794999999</v>
+        <v>-21.789107949999991</v>
       </c>
       <c r="D70" t="s">
         <v>95</v>
@@ -7531,15 +7609,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="71" spans="1:35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>8</v>
       </c>
       <c r="B71">
-        <v>-54.07309610000001</v>
+        <v>-54.073096100000008</v>
       </c>
       <c r="C71">
-        <v>-21.78910794999999</v>
+        <v>-21.789107949999991</v>
       </c>
       <c r="D71" t="s">
         <v>95</v>
@@ -7611,15 +7689,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="72" spans="1:35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>9</v>
       </c>
       <c r="B72">
-        <v>-54.07246620999999</v>
+        <v>-54.072466209999988</v>
       </c>
       <c r="C72">
-        <v>-21.78028646999996</v>
+        <v>-21.780286469999961</v>
       </c>
       <c r="D72" t="s">
         <v>96</v>
@@ -7691,15 +7769,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="73" spans="1:35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>9</v>
       </c>
       <c r="B73">
-        <v>-54.07246620999999</v>
+        <v>-54.072466209999988</v>
       </c>
       <c r="C73">
-        <v>-21.78028646999996</v>
+        <v>-21.780286469999961</v>
       </c>
       <c r="D73" t="s">
         <v>96</v>
@@ -7768,15 +7846,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="74" spans="1:35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10</v>
       </c>
       <c r="B74">
-        <v>-54.06839230000001</v>
+        <v>-54.068392300000014</v>
       </c>
       <c r="C74">
-        <v>-21.77968274000001</v>
+        <v>-21.779682740000009</v>
       </c>
       <c r="D74" t="s">
         <v>97</v>
@@ -7845,15 +7923,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="75" spans="1:35">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10</v>
       </c>
       <c r="B75">
-        <v>-54.06839230000001</v>
+        <v>-54.068392300000014</v>
       </c>
       <c r="C75">
-        <v>-21.77968274000001</v>
+        <v>-21.779682740000009</v>
       </c>
       <c r="D75" t="s">
         <v>97</v>
@@ -7922,15 +8000,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="76" spans="1:35">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>11</v>
       </c>
       <c r="B76">
-        <v>-54.06249565999997</v>
+        <v>-54.062495659999968</v>
       </c>
       <c r="C76">
-        <v>-21.77505509999999</v>
+        <v>-21.775055099999989</v>
       </c>
       <c r="D76" t="s">
         <v>98</v>
@@ -8002,15 +8080,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="77" spans="1:35">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>11</v>
       </c>
       <c r="B77">
-        <v>-54.06249565999997</v>
+        <v>-54.062495659999968</v>
       </c>
       <c r="C77">
-        <v>-21.77505509999999</v>
+        <v>-21.775055099999989</v>
       </c>
       <c r="D77" t="s">
         <v>98</v>
@@ -8079,15 +8157,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="78" spans="1:35">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>12</v>
       </c>
       <c r="B78">
-        <v>-54.06803117999998</v>
+        <v>-54.068031179999977</v>
       </c>
       <c r="C78">
-        <v>-21.77387780000001</v>
+        <v>-21.773877800000012</v>
       </c>
       <c r="D78" t="s">
         <v>99</v>
@@ -8156,15 +8234,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="79" spans="1:35">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>12</v>
       </c>
       <c r="B79">
-        <v>-54.06803117999998</v>
+        <v>-54.068031179999977</v>
       </c>
       <c r="C79">
-        <v>-21.77387780000001</v>
+        <v>-21.773877800000012</v>
       </c>
       <c r="D79" t="s">
         <v>99</v>
@@ -8233,12 +8311,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="80" spans="1:35">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>13</v>
       </c>
       <c r="B80">
-        <v>-54.1392985414009</v>
+        <v>-54.139298541400898</v>
       </c>
       <c r="C80">
         <v>-21.83575160196602</v>
@@ -8310,12 +8388,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="81" spans="1:35">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>13</v>
       </c>
       <c r="B81">
-        <v>-54.1392985414009</v>
+        <v>-54.139298541400898</v>
       </c>
       <c r="C81">
         <v>-21.83575160196602</v>
@@ -8387,7 +8465,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="82" spans="1:35">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>14</v>
       </c>
@@ -8395,7 +8473,7 @@
         <v>-53.99457771079468</v>
       </c>
       <c r="C82">
-        <v>-21.82080818533425</v>
+        <v>-21.820808185334251</v>
       </c>
       <c r="D82" t="s">
         <v>101</v>
@@ -8467,7 +8545,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="83" spans="1:35">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>14</v>
       </c>
@@ -8475,7 +8553,7 @@
         <v>-53.99457771079468</v>
       </c>
       <c r="C83">
-        <v>-21.82080818533425</v>
+        <v>-21.820808185334251</v>
       </c>
       <c r="D83" t="s">
         <v>101</v>
@@ -8547,7 +8625,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="84" spans="1:35">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>15</v>
       </c>
@@ -8555,7 +8633,7 @@
         <v>-53.98927520811889</v>
       </c>
       <c r="C84">
-        <v>-21.82080818533425</v>
+        <v>-21.820808185334251</v>
       </c>
       <c r="D84" t="s">
         <v>102</v>
@@ -8627,7 +8705,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="85" spans="1:35">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>15</v>
       </c>
@@ -8635,7 +8713,7 @@
         <v>-53.98927520811889</v>
       </c>
       <c r="C85">
-        <v>-21.82080818533425</v>
+        <v>-21.820808185334251</v>
       </c>
       <c r="D85" t="s">
         <v>102</v>
@@ -8704,15 +8782,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="86" spans="1:35">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>16</v>
       </c>
       <c r="B86">
-        <v>-53.99023929951451</v>
+        <v>-53.990239299514514</v>
       </c>
       <c r="C86">
-        <v>-21.82578932421153</v>
+        <v>-21.825789324211531</v>
       </c>
       <c r="D86" t="s">
         <v>103</v>
@@ -8781,15 +8859,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="87" spans="1:35">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>16</v>
       </c>
       <c r="B87">
-        <v>-53.99023929951451</v>
+        <v>-53.990239299514514</v>
       </c>
       <c r="C87">
-        <v>-21.82578932421153</v>
+        <v>-21.825789324211531</v>
       </c>
       <c r="D87" t="s">
         <v>103</v>
@@ -8858,7 +8936,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="88" spans="1:35">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>17</v>
       </c>
@@ -8935,7 +9013,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="89" spans="1:35">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>17</v>
       </c>
@@ -9012,15 +9090,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="90" spans="1:35">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>18</v>
       </c>
       <c r="B90">
-        <v>-53.9800092185945</v>
+        <v>-53.980009218594503</v>
       </c>
       <c r="C90">
-        <v>-21.82399504300306</v>
+        <v>-21.823995043003059</v>
       </c>
       <c r="D90" t="s">
         <v>105</v>
@@ -9089,15 +9167,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:35">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>18</v>
       </c>
       <c r="B91">
-        <v>-53.9800092185945</v>
+        <v>-53.980009218594503</v>
       </c>
       <c r="C91">
-        <v>-21.82399504300306</v>
+        <v>-21.823995043003059</v>
       </c>
       <c r="D91" t="s">
         <v>105</v>
@@ -9166,12 +9244,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="92" spans="1:35">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>19</v>
       </c>
       <c r="B92">
-        <v>-53.97904512719889</v>
+        <v>-53.979045127198887</v>
       </c>
       <c r="C92">
         <v>-21.82710155972217</v>
@@ -9246,12 +9324,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="93" spans="1:35">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>19</v>
       </c>
       <c r="B93">
-        <v>-53.97904512719889</v>
+        <v>-53.979045127198887</v>
       </c>
       <c r="C93">
         <v>-21.82710155972217</v>
@@ -9323,15 +9401,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="94" spans="1:35">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>20</v>
       </c>
       <c r="B94">
-        <v>-53.98630259298245</v>
+        <v>-53.986302592982447</v>
       </c>
       <c r="C94">
-        <v>-21.82628476006761</v>
+        <v>-21.826284760067612</v>
       </c>
       <c r="D94" t="s">
         <v>107</v>
@@ -9403,15 +9481,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="95" spans="1:35">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>20</v>
       </c>
       <c r="B95">
-        <v>-53.98630259298245</v>
+        <v>-53.986302592982447</v>
       </c>
       <c r="C95">
-        <v>-21.82628476006761</v>
+        <v>-21.826284760067612</v>
       </c>
       <c r="D95" t="s">
         <v>107</v>
@@ -9480,7 +9558,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="96" spans="1:35">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>21</v>
       </c>
@@ -9560,7 +9638,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="97" spans="1:35">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>21</v>
       </c>
@@ -9640,15 +9718,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="98" spans="1:35">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>22</v>
       </c>
       <c r="B98">
-        <v>-53.85669925106558</v>
+        <v>-53.856699251065578</v>
       </c>
       <c r="C98">
-        <v>-21.82201329957877</v>
+        <v>-21.822013299578771</v>
       </c>
       <c r="D98" t="s">
         <v>109</v>
@@ -9720,15 +9798,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="99" spans="1:35">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>22</v>
       </c>
       <c r="B99">
-        <v>-53.85669925106558</v>
+        <v>-53.856699251065578</v>
       </c>
       <c r="C99">
-        <v>-21.82201329957877</v>
+        <v>-21.822013299578771</v>
       </c>
       <c r="D99" t="s">
         <v>109</v>
@@ -9797,15 +9875,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="100" spans="1:35">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>23</v>
       </c>
       <c r="B100">
-        <v>-53.84839735293681</v>
+        <v>-53.848397352936807</v>
       </c>
       <c r="C100">
-        <v>-21.82011189710411</v>
+        <v>-21.820111897104109</v>
       </c>
       <c r="D100" t="s">
         <v>110</v>
@@ -9874,15 +9952,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="101" spans="1:35">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>23</v>
       </c>
       <c r="B101">
-        <v>-53.84839735293681</v>
+        <v>-53.848397352936807</v>
       </c>
       <c r="C101">
-        <v>-21.82011189710411</v>
+        <v>-21.820111897104109</v>
       </c>
       <c r="D101" t="s">
         <v>110</v>
@@ -9951,15 +10029,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="102" spans="1:35">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>24</v>
       </c>
       <c r="B102">
-        <v>-54.09607339020499</v>
+        <v>-54.096073390204992</v>
       </c>
       <c r="C102">
-        <v>-21.81080757306217</v>
+        <v>-21.810807573062171</v>
       </c>
       <c r="D102" t="s">
         <v>111</v>
@@ -10031,15 +10109,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="103" spans="1:35">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>24</v>
       </c>
       <c r="B103">
-        <v>-54.09607339020499</v>
+        <v>-54.096073390204992</v>
       </c>
       <c r="C103">
-        <v>-21.81080757306217</v>
+        <v>-21.810807573062171</v>
       </c>
       <c r="D103" t="s">
         <v>111</v>
@@ -10111,15 +10189,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:35">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>25</v>
       </c>
       <c r="B104">
-        <v>-54.09782441091689</v>
+        <v>-54.097824410916893</v>
       </c>
       <c r="C104">
-        <v>-21.80541981702561</v>
+        <v>-21.805419817025609</v>
       </c>
       <c r="D104" t="s">
         <v>112</v>
@@ -10191,15 +10269,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="105" spans="1:35">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>25</v>
       </c>
       <c r="B105">
-        <v>-54.09782441091689</v>
+        <v>-54.097824410916893</v>
       </c>
       <c r="C105">
-        <v>-21.80541981702561</v>
+        <v>-21.805419817025609</v>
       </c>
       <c r="D105" t="s">
         <v>112</v>
@@ -10268,15 +10346,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="106" spans="1:35">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>26</v>
       </c>
       <c r="B106">
-        <v>-54.09068563416844</v>
+        <v>-54.090685634168437</v>
       </c>
       <c r="C106">
-        <v>-21.80447695971924</v>
+        <v>-21.804476959719238</v>
       </c>
       <c r="D106" t="s">
         <v>113</v>
@@ -10345,15 +10423,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="107" spans="1:35">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>26</v>
       </c>
       <c r="B107">
-        <v>-54.09068563416844</v>
+        <v>-54.090685634168437</v>
       </c>
       <c r="C107">
-        <v>-21.80447695971924</v>
+        <v>-21.804476959719238</v>
       </c>
       <c r="D107" t="s">
         <v>113</v>
@@ -10422,15 +10500,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="108" spans="1:35">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>27</v>
       </c>
       <c r="B108">
-        <v>-54.09593869630407</v>
+        <v>-54.095938696304067</v>
       </c>
       <c r="C108">
-        <v>-21.80075042846065</v>
+        <v>-21.800750428460649</v>
       </c>
       <c r="D108" t="s">
         <v>114</v>
@@ -10499,15 +10577,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="109" spans="1:35">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>27</v>
       </c>
       <c r="B109">
-        <v>-54.09593869630407</v>
+        <v>-54.095938696304067</v>
       </c>
       <c r="C109">
-        <v>-21.80075042846065</v>
+        <v>-21.800750428460649</v>
       </c>
       <c r="D109" t="s">
         <v>114</v>
@@ -10576,12 +10654,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="110" spans="1:35">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>28</v>
       </c>
       <c r="B110">
-        <v>-54.10191820748305</v>
+        <v>-54.101918207483052</v>
       </c>
       <c r="C110">
         <v>-21.80807372032513</v>
@@ -10653,12 +10731,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="111" spans="1:35">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>28</v>
       </c>
       <c r="B111">
-        <v>-54.10191820748305</v>
+        <v>-54.101918207483052</v>
       </c>
       <c r="C111">
         <v>-21.80807372032513</v>
@@ -10730,15 +10808,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="112" spans="1:35">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>29</v>
       </c>
       <c r="B112">
-        <v>-54.10154115327801</v>
+        <v>-54.101541153278013</v>
       </c>
       <c r="C112">
-        <v>-21.81389624553576</v>
+        <v>-21.813896245535759</v>
       </c>
       <c r="D112" t="s">
         <v>116</v>
@@ -10810,15 +10888,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="113" spans="1:35">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>29</v>
       </c>
       <c r="B113">
-        <v>-54.10154115327801</v>
+        <v>-54.101541153278013</v>
       </c>
       <c r="C113">
-        <v>-21.81389624553576</v>
+        <v>-21.813896245535759</v>
       </c>
       <c r="D113" t="s">
         <v>116</v>
@@ -10887,15 +10965,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="114" spans="1:35">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>30</v>
       </c>
       <c r="B114">
-        <v>-54.11006065340774</v>
+        <v>-54.110060653407743</v>
       </c>
       <c r="C114">
-        <v>-21.81200321097564</v>
+        <v>-21.812003210975639</v>
       </c>
       <c r="D114" t="s">
         <v>117</v>
@@ -10964,15 +11042,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="115" spans="1:35">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>30</v>
       </c>
       <c r="B115">
-        <v>-54.11006065340774</v>
+        <v>-54.110060653407743</v>
       </c>
       <c r="C115">
-        <v>-21.81200321097564</v>
+        <v>-21.812003210975639</v>
       </c>
       <c r="D115" t="s">
         <v>117</v>
@@ -11041,15 +11119,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="116" spans="1:35">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>31</v>
       </c>
       <c r="B116">
-        <v>-54.11738001449593</v>
+        <v>-54.117380014495929</v>
       </c>
       <c r="C116">
-        <v>-21.81001024517</v>
+        <v>-21.810010245170002</v>
       </c>
       <c r="D116" t="s">
         <v>118</v>
@@ -11121,15 +11199,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="117" spans="1:35">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>31</v>
       </c>
       <c r="B117">
-        <v>-54.11738001449593</v>
+        <v>-54.117380014495929</v>
       </c>
       <c r="C117">
-        <v>-21.81001024517</v>
+        <v>-21.810010245170002</v>
       </c>
       <c r="D117" t="s">
         <v>118</v>
@@ -11198,15 +11276,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="118" spans="1:35">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>32</v>
       </c>
       <c r="B118">
-        <v>-54.11399633785985</v>
+        <v>-54.113996337859852</v>
       </c>
       <c r="C118">
-        <v>-21.80630805971865</v>
+        <v>-21.806308059718649</v>
       </c>
       <c r="D118" t="s">
         <v>119</v>
@@ -11275,15 +11353,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="119" spans="1:35">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>32</v>
       </c>
       <c r="B119">
-        <v>-54.11399633785985</v>
+        <v>-54.113996337859852</v>
       </c>
       <c r="C119">
-        <v>-21.80630805971865</v>
+        <v>-21.806308059718649</v>
       </c>
       <c r="D119" t="s">
         <v>119</v>
@@ -11352,12 +11430,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="120" spans="1:35">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>33</v>
       </c>
       <c r="B120">
-        <v>-54.31094603999996</v>
+        <v>-54.310946039999962</v>
       </c>
       <c r="C120">
         <v>-21.94287186999998</v>
@@ -11432,12 +11510,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="121" spans="1:35">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>33</v>
       </c>
       <c r="B121">
-        <v>-54.31094603999996</v>
+        <v>-54.310946039999962</v>
       </c>
       <c r="C121">
         <v>-21.94287186999998</v>
@@ -11512,15 +11590,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="122" spans="1:35">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>34</v>
       </c>
       <c r="B122">
-        <v>-54.30702394</v>
+        <v>-54.307023940000001</v>
       </c>
       <c r="C122">
-        <v>-21.9449087</v>
+        <v>-21.944908699999999</v>
       </c>
       <c r="D122" t="s">
         <v>121</v>
@@ -11592,15 +11670,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" spans="1:35">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>34</v>
       </c>
       <c r="B123">
-        <v>-54.30702394</v>
+        <v>-54.307023940000001</v>
       </c>
       <c r="C123">
-        <v>-21.9449087</v>
+        <v>-21.944908699999999</v>
       </c>
       <c r="D123" t="s">
         <v>121</v>
@@ -11669,15 +11747,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="124" spans="1:35">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>35</v>
       </c>
       <c r="B124">
-        <v>-54.31181149</v>
+        <v>-54.311811489999997</v>
       </c>
       <c r="C124">
-        <v>-21.94740382999998</v>
+        <v>-21.947403829999981</v>
       </c>
       <c r="D124" t="s">
         <v>122</v>
@@ -11746,15 +11824,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="125" spans="1:35">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>35</v>
       </c>
       <c r="B125">
-        <v>-54.31181149</v>
+        <v>-54.311811489999997</v>
       </c>
       <c r="C125">
-        <v>-21.94740382999998</v>
+        <v>-21.947403829999981</v>
       </c>
       <c r="D125" t="s">
         <v>122</v>
@@ -11823,12 +11901,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="126" spans="1:35">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>36</v>
       </c>
       <c r="B126">
-        <v>-54.31170200000002</v>
+        <v>-54.311702000000018</v>
       </c>
       <c r="C126">
         <v>-21.9526529</v>
@@ -11900,12 +11978,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="127" spans="1:35">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>36</v>
       </c>
       <c r="B127">
-        <v>-54.31170200000002</v>
+        <v>-54.311702000000018</v>
       </c>
       <c r="C127">
         <v>-21.9526529</v>
@@ -11977,12 +12055,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="128" spans="1:35">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>37</v>
       </c>
       <c r="B128">
-        <v>-54.31215926000002</v>
+        <v>-54.312159260000023</v>
       </c>
       <c r="C128">
         <v>-21.9564272</v>
@@ -12057,12 +12135,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="129" spans="1:35">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>37</v>
       </c>
       <c r="B129">
-        <v>-54.31215926000002</v>
+        <v>-54.312159260000023</v>
       </c>
       <c r="C129">
         <v>-21.9564272</v>
@@ -12134,7 +12212,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" spans="1:35">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>38</v>
       </c>
@@ -12142,7 +12220,7 @@
         <v>-54.30745666</v>
       </c>
       <c r="C130">
-        <v>-21.95532093999996</v>
+        <v>-21.955320939999961</v>
       </c>
       <c r="D130" t="s">
         <v>125</v>
@@ -12211,7 +12289,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="131" spans="1:35">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>38</v>
       </c>
@@ -12219,7 +12297,7 @@
         <v>-54.30745666</v>
       </c>
       <c r="C131">
-        <v>-21.95532093999996</v>
+        <v>-21.955320939999961</v>
       </c>
       <c r="D131" t="s">
         <v>125</v>
@@ -12288,15 +12366,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="132" spans="1:35">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>39</v>
       </c>
       <c r="B132">
-        <v>-54.30527145999998</v>
+        <v>-54.305271459999979</v>
       </c>
       <c r="C132">
-        <v>-21.95232981999997</v>
+        <v>-21.952329819999971</v>
       </c>
       <c r="D132" t="s">
         <v>126</v>
@@ -12368,15 +12446,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" spans="1:35">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>39</v>
       </c>
       <c r="B133">
-        <v>-54.30527145999998</v>
+        <v>-54.305271459999979</v>
       </c>
       <c r="C133">
-        <v>-21.95232981999997</v>
+        <v>-21.952329819999971</v>
       </c>
       <c r="D133" t="s">
         <v>126</v>
@@ -12445,12 +12523,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="134" spans="1:35">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>40</v>
       </c>
       <c r="B134">
-        <v>-54.30294402000001</v>
+        <v>-54.302944020000012</v>
       </c>
       <c r="C134">
         <v>-21.94909104000002</v>
@@ -12522,12 +12600,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="135" spans="1:35">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>40</v>
       </c>
       <c r="B135">
-        <v>-54.30294402000001</v>
+        <v>-54.302944020000012</v>
       </c>
       <c r="C135">
         <v>-21.94909104000002</v>
@@ -12599,15 +12677,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="136" spans="1:35">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>41</v>
       </c>
       <c r="B136">
-        <v>-54.30002254000001</v>
+        <v>-54.300022540000008</v>
       </c>
       <c r="C136">
-        <v>-21.95397246</v>
+        <v>-21.953972459999999</v>
       </c>
       <c r="D136" t="s">
         <v>128</v>
@@ -12676,15 +12754,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="137" spans="1:35">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>41</v>
       </c>
       <c r="B137">
-        <v>-54.30002254000001</v>
+        <v>-54.300022540000008</v>
       </c>
       <c r="C137">
-        <v>-21.95397246</v>
+        <v>-21.953972459999999</v>
       </c>
       <c r="D137" t="s">
         <v>128</v>
@@ -12753,12 +12831,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="138" spans="1:35">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>42</v>
       </c>
       <c r="B138">
-        <v>-54.30270097000001</v>
+        <v>-54.302700970000011</v>
       </c>
       <c r="C138">
         <v>-21.95788427999998</v>
@@ -12833,12 +12911,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="139" spans="1:35">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>42</v>
       </c>
       <c r="B139">
-        <v>-54.30270097000001</v>
+        <v>-54.302700970000011</v>
       </c>
       <c r="C139">
         <v>-21.95788427999998</v>
@@ -12910,15 +12988,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="140" spans="1:35">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>43</v>
       </c>
       <c r="B140">
-        <v>-54.29510326999998</v>
+        <v>-54.295103269999977</v>
       </c>
       <c r="C140">
-        <v>-21.95551857</v>
+        <v>-21.955518569999999</v>
       </c>
       <c r="D140" t="s">
         <v>130</v>
@@ -12990,15 +13068,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="141" spans="1:35">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>43</v>
       </c>
       <c r="B141">
-        <v>-54.29510326999998</v>
+        <v>-54.295103269999977</v>
       </c>
       <c r="C141">
-        <v>-21.95551857</v>
+        <v>-21.955518569999999</v>
       </c>
       <c r="D141" t="s">
         <v>130</v>
@@ -13067,15 +13145,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="142" spans="1:35">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>44</v>
       </c>
       <c r="B142">
-        <v>-54.29190398000001</v>
+        <v>-54.291903980000008</v>
       </c>
       <c r="C142">
-        <v>-21.95707181999997</v>
+        <v>-21.957071819999971</v>
       </c>
       <c r="D142" t="s">
         <v>131</v>
@@ -13144,15 +13222,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="143" spans="1:35">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>44</v>
       </c>
       <c r="B143">
-        <v>-54.29190398000001</v>
+        <v>-54.291903980000008</v>
       </c>
       <c r="C143">
-        <v>-21.95707181999997</v>
+        <v>-21.957071819999971</v>
       </c>
       <c r="D143" t="s">
         <v>131</v>
@@ -13221,12 +13299,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="144" spans="1:35">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>45</v>
       </c>
       <c r="B144">
-        <v>-54.28694239000001</v>
+        <v>-54.286942390000007</v>
       </c>
       <c r="C144">
         <v>-21.95819793999998</v>
@@ -13301,12 +13379,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="145" spans="1:35">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>45</v>
       </c>
       <c r="B145">
-        <v>-54.28694239000001</v>
+        <v>-54.286942390000007</v>
       </c>
       <c r="C145">
         <v>-21.95819793999998</v>
@@ -13378,15 +13456,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="146" spans="1:35">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>46</v>
       </c>
       <c r="B146">
-        <v>-54.28296232999998</v>
+        <v>-54.282962329999982</v>
       </c>
       <c r="C146">
-        <v>-21.96431577999997</v>
+        <v>-21.964315779999971</v>
       </c>
       <c r="D146" t="s">
         <v>133</v>
@@ -13455,15 +13533,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="147" spans="1:35">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>46</v>
       </c>
       <c r="B147">
-        <v>-54.28296232999998</v>
+        <v>-54.282962329999982</v>
       </c>
       <c r="C147">
-        <v>-21.96431577999997</v>
+        <v>-21.964315779999971</v>
       </c>
       <c r="D147" t="s">
         <v>133</v>
@@ -13532,15 +13610,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="148" spans="1:35">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>47</v>
       </c>
       <c r="B148">
-        <v>-54.28294957000001</v>
+        <v>-54.282949570000007</v>
       </c>
       <c r="C148">
-        <v>-21.96689540999999</v>
+        <v>-21.966895409999989</v>
       </c>
       <c r="D148" t="s">
         <v>134</v>
@@ -13612,15 +13690,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="149" spans="1:35">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>47</v>
       </c>
       <c r="B149">
-        <v>-54.28294957000001</v>
+        <v>-54.282949570000007</v>
       </c>
       <c r="C149">
-        <v>-21.96689540999999</v>
+        <v>-21.966895409999989</v>
       </c>
       <c r="D149" t="s">
         <v>134</v>
@@ -13689,12 +13767,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="150" spans="1:35">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>48</v>
       </c>
       <c r="B150">
-        <v>-54.28543263</v>
+        <v>-54.285432630000003</v>
       </c>
       <c r="C150">
         <v>-21.97145023999996</v>
@@ -13766,12 +13844,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="151" spans="1:35">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>48</v>
       </c>
       <c r="B151">
-        <v>-54.28543263</v>
+        <v>-54.285432630000003</v>
       </c>
       <c r="C151">
         <v>-21.97145023999996</v>
@@ -13843,15 +13921,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="152" spans="1:35">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>49</v>
       </c>
       <c r="B152">
-        <v>-54.28623609</v>
+        <v>-54.286236090000003</v>
       </c>
       <c r="C152">
-        <v>-21.96478106999998</v>
+        <v>-21.964781069999979</v>
       </c>
       <c r="D152" t="s">
         <v>136</v>
@@ -13920,15 +13998,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="153" spans="1:35">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>49</v>
       </c>
       <c r="B153">
-        <v>-54.28623609</v>
+        <v>-54.286236090000003</v>
       </c>
       <c r="C153">
-        <v>-21.96478106999998</v>
+        <v>-21.964781069999979</v>
       </c>
       <c r="D153" t="s">
         <v>136</v>
@@ -13997,15 +14075,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="154" spans="1:35">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>50</v>
       </c>
       <c r="B154">
-        <v>-54.29072586999997</v>
+        <v>-54.290725869999967</v>
       </c>
       <c r="C154">
-        <v>-21.96381164000002</v>
+        <v>-21.963811640000021</v>
       </c>
       <c r="D154" t="s">
         <v>137</v>
@@ -14074,15 +14152,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="155" spans="1:35">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>50</v>
       </c>
       <c r="B155">
-        <v>-54.29072586999997</v>
+        <v>-54.290725869999967</v>
       </c>
       <c r="C155">
-        <v>-21.96381164000002</v>
+        <v>-21.963811640000021</v>
       </c>
       <c r="D155" t="s">
         <v>137</v>
@@ -14151,15 +14229,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="156" spans="1:35">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>51</v>
       </c>
       <c r="B156">
-        <v>-54.29419908000001</v>
+        <v>-54.294199080000013</v>
       </c>
       <c r="C156">
-        <v>-21.96203244999998</v>
+        <v>-21.962032449999981</v>
       </c>
       <c r="D156" t="s">
         <v>138</v>
@@ -14228,15 +14306,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="157" spans="1:35">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>51</v>
       </c>
       <c r="B157">
-        <v>-54.29419908000001</v>
+        <v>-54.294199080000013</v>
       </c>
       <c r="C157">
-        <v>-21.96203244999998</v>
+        <v>-21.962032449999981</v>
       </c>
       <c r="D157" t="s">
         <v>138</v>
@@ -14305,7 +14383,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="158" spans="1:35">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>52</v>
       </c>
@@ -14313,7 +14391,7 @@
         <v>-54.29811021999997</v>
       </c>
       <c r="C158">
-        <v>-21.95975096000001</v>
+        <v>-21.959750960000012</v>
       </c>
       <c r="D158" t="s">
         <v>139</v>
@@ -14382,7 +14460,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="159" spans="1:35">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>52</v>
       </c>
@@ -14390,7 +14468,7 @@
         <v>-54.29811021999997</v>
       </c>
       <c r="C159">
-        <v>-21.95975096000001</v>
+        <v>-21.959750960000012</v>
       </c>
       <c r="D159" t="s">
         <v>139</v>
@@ -14459,12 +14537,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="160" spans="1:35">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>53</v>
       </c>
       <c r="B160">
-        <v>-54.29310460999996</v>
+        <v>-54.293104609999958</v>
       </c>
       <c r="C160">
         <v>-21.96736975000001</v>
@@ -14539,12 +14617,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="161" spans="1:35">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>53</v>
       </c>
       <c r="B161">
-        <v>-54.29310460999996</v>
+        <v>-54.293104609999958</v>
       </c>
       <c r="C161">
         <v>-21.96736975000001</v>
@@ -14616,7 +14694,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="162" spans="1:35">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>54</v>
       </c>
@@ -14624,7 +14702,7 @@
         <v>-54.29717373999997</v>
       </c>
       <c r="C162">
-        <v>-21.96540184</v>
+        <v>-21.965401839999998</v>
       </c>
       <c r="D162" t="s">
         <v>141</v>
@@ -14693,7 +14771,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="163" spans="1:35">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>54</v>
       </c>
@@ -14701,7 +14779,7 @@
         <v>-54.29717373999997</v>
       </c>
       <c r="C163">
-        <v>-21.96540184</v>
+        <v>-21.965401839999998</v>
       </c>
       <c r="D163" t="s">
         <v>141</v>
@@ -14770,12 +14848,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="164" spans="1:35">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>55</v>
       </c>
       <c r="B164">
-        <v>-54.30162116644279</v>
+        <v>-54.301621166442793</v>
       </c>
       <c r="C164">
         <v>-21.9625051373242</v>
@@ -14847,12 +14925,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="165" spans="1:35">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>55</v>
       </c>
       <c r="B165">
-        <v>-54.30162116644279</v>
+        <v>-54.301621166442793</v>
       </c>
       <c r="C165">
         <v>-21.9625051373242</v>
@@ -14924,15 +15002,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="166" spans="1:35">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>56</v>
       </c>
       <c r="B166">
-        <v>-54.30431258000001</v>
+        <v>-54.304312580000008</v>
       </c>
       <c r="C166">
-        <v>-21.96098690000001</v>
+        <v>-21.960986900000009</v>
       </c>
       <c r="D166" t="s">
         <v>143</v>
@@ -15001,15 +15079,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="167" spans="1:35">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>56</v>
       </c>
       <c r="B167">
-        <v>-54.30431258000001</v>
+        <v>-54.304312580000008</v>
       </c>
       <c r="C167">
-        <v>-21.96098690000001</v>
+        <v>-21.960986900000009</v>
       </c>
       <c r="D167" t="s">
         <v>143</v>
@@ -15078,15 +15156,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="168" spans="1:35">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>57</v>
       </c>
       <c r="B168">
-        <v>-54.30337822999997</v>
+        <v>-54.303378229999971</v>
       </c>
       <c r="C168">
-        <v>-21.96707212999996</v>
+        <v>-21.967072129999959</v>
       </c>
       <c r="D168" t="s">
         <v>144</v>
@@ -15158,15 +15236,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="169" spans="1:35">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>57</v>
       </c>
       <c r="B169">
-        <v>-54.30337822999997</v>
+        <v>-54.303378229999971</v>
       </c>
       <c r="C169">
-        <v>-21.96707212999996</v>
+        <v>-21.967072129999959</v>
       </c>
       <c r="D169" t="s">
         <v>144</v>
@@ -15235,12 +15313,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="170" spans="1:35">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>58</v>
       </c>
       <c r="B170">
-        <v>-54.30678914999998</v>
+        <v>-54.306789149999979</v>
       </c>
       <c r="C170">
         <v>-21.96349994999996</v>
@@ -15312,12 +15390,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="171" spans="1:35">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>58</v>
       </c>
       <c r="B171">
-        <v>-54.30678914999998</v>
+        <v>-54.306789149999979</v>
       </c>
       <c r="C171">
         <v>-21.96349994999996</v>
@@ -15389,15 +15467,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="172" spans="1:35">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>59</v>
       </c>
       <c r="B172">
-        <v>-54.31226564999999</v>
+        <v>-54.312265649999993</v>
       </c>
       <c r="C172">
-        <v>-21.96255738999998</v>
+        <v>-21.962557389999979</v>
       </c>
       <c r="D172" t="s">
         <v>146</v>
@@ -15466,15 +15544,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="173" spans="1:35">
+    <row r="173" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>59</v>
       </c>
       <c r="B173">
-        <v>-54.31226564999999</v>
+        <v>-54.312265649999993</v>
       </c>
       <c r="C173">
-        <v>-21.96255738999998</v>
+        <v>-21.962557389999979</v>
       </c>
       <c r="D173" t="s">
         <v>146</v>
@@ -15543,15 +15621,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="174" spans="1:35">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>60</v>
       </c>
       <c r="B174">
-        <v>-54.31298083000001</v>
+        <v>-54.312980830000008</v>
       </c>
       <c r="C174">
-        <v>-21.96807027999999</v>
+        <v>-21.968070279999989</v>
       </c>
       <c r="D174" t="s">
         <v>147</v>
@@ -15623,15 +15701,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="175" spans="1:35">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>60</v>
       </c>
       <c r="B175">
-        <v>-54.31298083000001</v>
+        <v>-54.312980830000008</v>
       </c>
       <c r="C175">
-        <v>-21.96807027999999</v>
+        <v>-21.968070279999989</v>
       </c>
       <c r="D175" t="s">
         <v>147</v>
@@ -15700,15 +15778,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="176" spans="1:35">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>61</v>
       </c>
       <c r="B176">
-        <v>-54.30877181999996</v>
+        <v>-54.308771819999961</v>
       </c>
       <c r="C176">
-        <v>-21.96903363999997</v>
+        <v>-21.969033639999971</v>
       </c>
       <c r="D176" t="s">
         <v>148</v>
@@ -15777,15 +15855,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="177" spans="1:35">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>61</v>
       </c>
       <c r="B177">
-        <v>-54.30877181999996</v>
+        <v>-54.308771819999961</v>
       </c>
       <c r="C177">
-        <v>-21.96903363999997</v>
+        <v>-21.969033639999971</v>
       </c>
       <c r="D177" t="s">
         <v>148</v>
@@ -15854,15 +15932,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="178" spans="1:35">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>62</v>
       </c>
       <c r="B178">
-        <v>-54.31186485000001</v>
+        <v>-54.311864850000013</v>
       </c>
       <c r="C178">
-        <v>-21.97159976000001</v>
+        <v>-21.971599760000011</v>
       </c>
       <c r="D178" t="s">
         <v>149</v>
@@ -15931,15 +16009,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="179" spans="1:35">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>62</v>
       </c>
       <c r="B179">
-        <v>-54.31186485000001</v>
+        <v>-54.311864850000013</v>
       </c>
       <c r="C179">
-        <v>-21.97159976000001</v>
+        <v>-21.971599760000011</v>
       </c>
       <c r="D179" t="s">
         <v>149</v>
@@ -16008,15 +16086,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="180" spans="1:35">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>63</v>
       </c>
       <c r="B180">
-        <v>-54.30498908000001</v>
+        <v>-54.304989080000013</v>
       </c>
       <c r="C180">
-        <v>-21.97189644999997</v>
+        <v>-21.971896449999971</v>
       </c>
       <c r="D180" t="s">
         <v>150</v>
@@ -16085,15 +16163,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="181" spans="1:35">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>63</v>
       </c>
       <c r="B181">
-        <v>-54.30498908000001</v>
+        <v>-54.304989080000013</v>
       </c>
       <c r="C181">
-        <v>-21.97189644999997</v>
+        <v>-21.971896449999971</v>
       </c>
       <c r="D181" t="s">
         <v>150</v>
@@ -16162,12 +16240,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="182" spans="1:35">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>64</v>
       </c>
       <c r="B182">
-        <v>-54.30688134999998</v>
+        <v>-54.306881349999983</v>
       </c>
       <c r="C182">
         <v>-21.97458922999996</v>
@@ -16242,12 +16320,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="183" spans="1:35">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>64</v>
       </c>
       <c r="B183">
-        <v>-54.30688134999998</v>
+        <v>-54.306881349999983</v>
       </c>
       <c r="C183">
         <v>-21.97458922999996</v>
@@ -16319,12 +16397,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="184" spans="1:35">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>65</v>
       </c>
       <c r="B184">
-        <v>-54.31422209000002</v>
+        <v>-54.314222090000023</v>
       </c>
       <c r="C184">
         <v>-21.97680217000001</v>
@@ -16396,12 +16474,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="185" spans="1:35">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>65</v>
       </c>
       <c r="B185">
-        <v>-54.31422209000002</v>
+        <v>-54.314222090000023</v>
       </c>
       <c r="C185">
         <v>-21.97680217000001</v>
@@ -16473,12 +16551,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="186" spans="1:35">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>66</v>
       </c>
       <c r="B186">
-        <v>-54.31954726999997</v>
+        <v>-54.319547269999973</v>
       </c>
       <c r="C186">
         <v>-21.97653893</v>
@@ -16553,12 +16631,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="187" spans="1:35">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>66</v>
       </c>
       <c r="B187">
-        <v>-54.31954726999997</v>
+        <v>-54.319547269999973</v>
       </c>
       <c r="C187">
         <v>-21.97653893</v>
@@ -16630,15 +16708,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="188" spans="1:35">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>67</v>
       </c>
       <c r="B188">
-        <v>-54.31835405999997</v>
+        <v>-54.318354059999969</v>
       </c>
       <c r="C188">
-        <v>-21.98699142</v>
+        <v>-21.986991419999999</v>
       </c>
       <c r="D188" t="s">
         <v>154</v>
@@ -16707,15 +16785,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="189" spans="1:35">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>67</v>
       </c>
       <c r="B189">
-        <v>-54.31835405999997</v>
+        <v>-54.318354059999969</v>
       </c>
       <c r="C189">
-        <v>-21.98699142</v>
+        <v>-21.986991419999999</v>
       </c>
       <c r="D189" t="s">
         <v>154</v>
@@ -16784,15 +16862,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="190" spans="1:35">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>68</v>
       </c>
       <c r="B190">
-        <v>-54.32004027999998</v>
+        <v>-54.320040279999979</v>
       </c>
       <c r="C190">
-        <v>-21.98978367999998</v>
+        <v>-21.989783679999981</v>
       </c>
       <c r="D190" t="s">
         <v>155</v>
@@ -16861,15 +16939,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="191" spans="1:35">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>68</v>
       </c>
       <c r="B191">
-        <v>-54.32004027999998</v>
+        <v>-54.320040279999979</v>
       </c>
       <c r="C191">
-        <v>-21.98978367999998</v>
+        <v>-21.989783679999981</v>
       </c>
       <c r="D191" t="s">
         <v>155</v>
@@ -16938,12 +17016,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="192" spans="1:35">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>69</v>
       </c>
       <c r="B192">
-        <v>-54.31644229999998</v>
+        <v>-54.316442299999977</v>
       </c>
       <c r="C192">
         <v>-21.99117681000002</v>
@@ -17018,12 +17096,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="193" spans="1:35">
+    <row r="193" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>69</v>
       </c>
       <c r="B193">
-        <v>-54.31644229999998</v>
+        <v>-54.316442299999977</v>
       </c>
       <c r="C193">
         <v>-21.99117681000002</v>
@@ -17095,15 +17173,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="194" spans="1:35">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>70</v>
       </c>
       <c r="B194">
-        <v>-54.31097640999997</v>
+        <v>-54.310976409999967</v>
       </c>
       <c r="C194">
-        <v>-21.99317155999998</v>
+        <v>-21.993171559999979</v>
       </c>
       <c r="D194" t="s">
         <v>157</v>
@@ -17172,15 +17250,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="195" spans="1:35">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>70</v>
       </c>
       <c r="B195">
-        <v>-54.31097640999997</v>
+        <v>-54.310976409999967</v>
       </c>
       <c r="C195">
-        <v>-21.99317155999998</v>
+        <v>-21.993171559999979</v>
       </c>
       <c r="D195" t="s">
         <v>157</v>
@@ -17249,7 +17327,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="196" spans="1:35">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>71</v>
       </c>
@@ -17257,7 +17335,7 @@
         <v>-54.30270711911853</v>
       </c>
       <c r="C196">
-        <v>-21.98946341999997</v>
+        <v>-21.989463419999971</v>
       </c>
       <c r="D196" t="s">
         <v>158</v>
@@ -17329,7 +17407,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="197" spans="1:35">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>71</v>
       </c>
@@ -17337,7 +17415,7 @@
         <v>-54.30270711911853</v>
       </c>
       <c r="C197">
-        <v>-21.98946341999997</v>
+        <v>-21.989463419999971</v>
       </c>
       <c r="D197" t="s">
         <v>158</v>
@@ -17406,15 +17484,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="198" spans="1:35">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>72</v>
       </c>
       <c r="B198">
-        <v>-54.29830302000001</v>
+        <v>-54.298303020000013</v>
       </c>
       <c r="C198">
-        <v>-21.99149972999996</v>
+        <v>-21.991499729999958</v>
       </c>
       <c r="D198" t="s">
         <v>159</v>
@@ -17483,15 +17561,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="199" spans="1:35">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>72</v>
       </c>
       <c r="B199">
-        <v>-54.29830302000001</v>
+        <v>-54.298303020000013</v>
       </c>
       <c r="C199">
-        <v>-21.99149972999996</v>
+        <v>-21.991499729999958</v>
       </c>
       <c r="D199" t="s">
         <v>159</v>
@@ -17560,15 +17638,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="200" spans="1:35">
+    <row r="200" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>73</v>
       </c>
       <c r="B200">
-        <v>-54.3026237747744</v>
+        <v>-54.302623774774403</v>
       </c>
       <c r="C200">
-        <v>-21.99624968348376</v>
+        <v>-21.996249683483761</v>
       </c>
       <c r="D200" t="s">
         <v>160</v>
@@ -17637,15 +17715,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="201" spans="1:35">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>73</v>
       </c>
       <c r="B201">
-        <v>-54.3026237747744</v>
+        <v>-54.302623774774403</v>
       </c>
       <c r="C201">
-        <v>-21.99624968348376</v>
+        <v>-21.996249683483761</v>
       </c>
       <c r="D201" t="s">
         <v>160</v>
@@ -17714,12 +17792,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="202" spans="1:35">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>74</v>
       </c>
       <c r="B202">
-        <v>-54.29761804</v>
+        <v>-54.297618040000003</v>
       </c>
       <c r="C202">
         <v>-21.99820884</v>
@@ -17794,12 +17872,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="203" spans="1:35">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>74</v>
       </c>
       <c r="B203">
-        <v>-54.29761804</v>
+        <v>-54.297618040000003</v>
       </c>
       <c r="C203">
         <v>-21.99820884</v>
@@ -17871,12 +17949,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="204" spans="1:35">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>75</v>
       </c>
       <c r="B204">
-        <v>-54.35638764999998</v>
+        <v>-54.356387649999981</v>
       </c>
       <c r="C204">
         <v>-22.00742730000001</v>
@@ -17951,12 +18029,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="205" spans="1:35">
+    <row r="205" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>75</v>
       </c>
       <c r="B205">
-        <v>-54.35638764999998</v>
+        <v>-54.356387649999981</v>
       </c>
       <c r="C205">
         <v>-22.00742730000001</v>
@@ -18031,15 +18109,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="206" spans="1:35">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>76</v>
       </c>
       <c r="B206">
-        <v>-54.35308421999999</v>
+        <v>-54.353084219999992</v>
       </c>
       <c r="C206">
-        <v>-22.00978833999996</v>
+        <v>-22.009788339999961</v>
       </c>
       <c r="D206" t="s">
         <v>163</v>
@@ -18111,15 +18189,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="207" spans="1:35">
+    <row r="207" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>76</v>
       </c>
       <c r="B207">
-        <v>-54.35308421999999</v>
+        <v>-54.353084219999992</v>
       </c>
       <c r="C207">
-        <v>-22.00978833999996</v>
+        <v>-22.009788339999961</v>
       </c>
       <c r="D207" t="s">
         <v>163</v>
@@ -18188,7 +18266,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="208" spans="1:35">
+    <row r="208" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>77</v>
       </c>
@@ -18265,7 +18343,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="209" spans="1:35">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>77</v>
       </c>
@@ -18342,15 +18420,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="210" spans="1:35">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>78</v>
       </c>
       <c r="B210">
-        <v>-54.34214790999999</v>
+        <v>-54.342147909999987</v>
       </c>
       <c r="C210">
-        <v>-22.01307759000001</v>
+        <v>-22.013077590000009</v>
       </c>
       <c r="D210" t="s">
         <v>165</v>
@@ -18419,15 +18497,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="211" spans="1:35">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>78</v>
       </c>
       <c r="B211">
-        <v>-54.34214790999999</v>
+        <v>-54.342147909999987</v>
       </c>
       <c r="C211">
-        <v>-22.01307759000001</v>
+        <v>-22.013077590000009</v>
       </c>
       <c r="D211" t="s">
         <v>165</v>
@@ -18496,12 +18574,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="212" spans="1:35">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>79</v>
       </c>
       <c r="B212">
-        <v>-54.33815509999997</v>
+        <v>-54.338155099999973</v>
       </c>
       <c r="C212">
         <v>-22.01637263999999</v>
@@ -18573,12 +18651,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="213" spans="1:35">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>79</v>
       </c>
       <c r="B213">
-        <v>-54.33815509999997</v>
+        <v>-54.338155099999973</v>
       </c>
       <c r="C213">
         <v>-22.01637263999999</v>
@@ -18650,15 +18728,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="214" spans="1:35">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>80</v>
       </c>
       <c r="B214">
-        <v>-54.33725465999999</v>
+        <v>-54.337254659999992</v>
       </c>
       <c r="C214">
-        <v>-22.01258538999999</v>
+        <v>-22.012585389999991</v>
       </c>
       <c r="D214" t="s">
         <v>167</v>
@@ -18727,15 +18805,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="215" spans="1:35">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>80</v>
       </c>
       <c r="B215">
-        <v>-54.33725465999999</v>
+        <v>-54.337254659999992</v>
       </c>
       <c r="C215">
-        <v>-22.01258538999999</v>
+        <v>-22.012585389999991</v>
       </c>
       <c r="D215" t="s">
         <v>167</v>
@@ -18804,15 +18882,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="216" spans="1:35">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>81</v>
       </c>
       <c r="B216">
-        <v>-54.32775717999998</v>
+        <v>-54.327757179999978</v>
       </c>
       <c r="C216">
-        <v>-22.01681111999999</v>
+        <v>-22.016811119999989</v>
       </c>
       <c r="D216" t="s">
         <v>168</v>
@@ -18881,15 +18959,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="217" spans="1:35">
+    <row r="217" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>81</v>
       </c>
       <c r="B217">
-        <v>-54.32775717999998</v>
+        <v>-54.327757179999978</v>
       </c>
       <c r="C217">
-        <v>-22.01681111999999</v>
+        <v>-22.016811119999989</v>
       </c>
       <c r="D217" t="s">
         <v>168</v>
@@ -18958,12 +19036,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="218" spans="1:35">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>82</v>
       </c>
       <c r="B218">
-        <v>-54.32144862999999</v>
+        <v>-54.321448629999992</v>
       </c>
       <c r="C218">
         <v>-22.01933101000003</v>
@@ -19038,12 +19116,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="219" spans="1:35">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>82</v>
       </c>
       <c r="B219">
-        <v>-54.32144862999999</v>
+        <v>-54.321448629999992</v>
       </c>
       <c r="C219">
         <v>-22.01933101000003</v>
@@ -19115,12 +19193,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="220" spans="1:35">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>83</v>
       </c>
       <c r="B220">
-        <v>-54.31637674</v>
+        <v>-54.316376740000003</v>
       </c>
       <c r="C220">
         <v>-22.01128482</v>
@@ -19192,12 +19270,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="221" spans="1:35">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>83</v>
       </c>
       <c r="B221">
-        <v>-54.31637674</v>
+        <v>-54.316376740000003</v>
       </c>
       <c r="C221">
         <v>-22.01128482</v>
@@ -19269,15 +19347,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="222" spans="1:35">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>84</v>
       </c>
       <c r="B222">
-        <v>-54.31785226</v>
+        <v>-54.317852260000002</v>
       </c>
       <c r="C222">
-        <v>-22.00821784000001</v>
+        <v>-22.008217840000011</v>
       </c>
       <c r="D222" t="s">
         <v>171</v>
@@ -19346,15 +19424,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="223" spans="1:35">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>84</v>
       </c>
       <c r="B223">
-        <v>-54.31785226</v>
+        <v>-54.317852260000002</v>
       </c>
       <c r="C223">
-        <v>-22.00821784000001</v>
+        <v>-22.008217840000011</v>
       </c>
       <c r="D223" t="s">
         <v>171</v>
@@ -19423,15 +19501,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="224" spans="1:35">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>85</v>
       </c>
       <c r="B224">
-        <v>-54.31179607999999</v>
+        <v>-54.311796079999993</v>
       </c>
       <c r="C224">
-        <v>-22.00582896</v>
+        <v>-22.005828959999999</v>
       </c>
       <c r="D224" t="s">
         <v>172</v>
@@ -19503,15 +19581,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="225" spans="1:35">
+    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>85</v>
       </c>
       <c r="B225">
-        <v>-54.31179607999999</v>
+        <v>-54.311796079999993</v>
       </c>
       <c r="C225">
-        <v>-22.00582896</v>
+        <v>-22.005828959999999</v>
       </c>
       <c r="D225" t="s">
         <v>172</v>
@@ -19580,15 +19658,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="226" spans="1:35">
+    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>86</v>
       </c>
       <c r="B226">
-        <v>-54.31615464000001</v>
+        <v>-54.316154640000008</v>
       </c>
       <c r="C226">
-        <v>-22.00257115999995</v>
+        <v>-22.002571159999949</v>
       </c>
       <c r="D226" t="s">
         <v>173</v>
@@ -19657,15 +19735,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="227" spans="1:35">
+    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>86</v>
       </c>
       <c r="B227">
-        <v>-54.31615464000001</v>
+        <v>-54.316154640000008</v>
       </c>
       <c r="C227">
-        <v>-22.00257115999995</v>
+        <v>-22.002571159999949</v>
       </c>
       <c r="D227" t="s">
         <v>173</v>
@@ -19734,15 +19812,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="228" spans="1:35">
+    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>87</v>
       </c>
       <c r="B228">
-        <v>-54.32307990999995</v>
+        <v>-54.323079909999947</v>
       </c>
       <c r="C228">
-        <v>-22.00292861000001</v>
+        <v>-22.002928610000009</v>
       </c>
       <c r="D228" t="s">
         <v>174</v>
@@ -19814,15 +19892,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="229" spans="1:35">
+    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>87</v>
       </c>
       <c r="B229">
-        <v>-54.32307990999995</v>
+        <v>-54.323079909999947</v>
       </c>
       <c r="C229">
-        <v>-22.00292861000001</v>
+        <v>-22.002928610000009</v>
       </c>
       <c r="D229" t="s">
         <v>174</v>
@@ -19891,15 +19969,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="230" spans="1:35">
+    <row r="230" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>88</v>
       </c>
       <c r="B230">
-        <v>-54.32591575000001</v>
+        <v>-54.325915750000007</v>
       </c>
       <c r="C230">
-        <v>-22.00047879999997</v>
+        <v>-22.000478799999971</v>
       </c>
       <c r="D230" t="s">
         <v>175</v>
@@ -19968,15 +20046,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="231" spans="1:35">
+    <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>88</v>
       </c>
       <c r="B231">
-        <v>-54.32591575000001</v>
+        <v>-54.325915750000007</v>
       </c>
       <c r="C231">
-        <v>-22.00047879999997</v>
+        <v>-22.000478799999971</v>
       </c>
       <c r="D231" t="s">
         <v>175</v>
@@ -20045,15 +20123,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="232" spans="1:35">
+    <row r="232" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>89</v>
       </c>
       <c r="B232">
-        <v>-54.33032256999998</v>
+        <v>-54.330322569999979</v>
       </c>
       <c r="C232">
-        <v>-22.00018394999998</v>
+        <v>-22.000183949999979</v>
       </c>
       <c r="D232" t="s">
         <v>176</v>
@@ -20122,15 +20200,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="233" spans="1:35">
+    <row r="233" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>89</v>
       </c>
       <c r="B233">
-        <v>-54.33032256999998</v>
+        <v>-54.330322569999979</v>
       </c>
       <c r="C233">
-        <v>-22.00018394999998</v>
+        <v>-22.000183949999979</v>
       </c>
       <c r="D233" t="s">
         <v>176</v>
@@ -20199,15 +20277,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="234" spans="1:35">
+    <row r="234" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>90</v>
       </c>
       <c r="B234">
-        <v>-54.33070336000002</v>
+        <v>-54.330703360000022</v>
       </c>
       <c r="C234">
-        <v>-22.00429456000001</v>
+        <v>-22.004294560000009</v>
       </c>
       <c r="D234" t="s">
         <v>177</v>
@@ -20276,15 +20354,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="235" spans="1:35">
+    <row r="235" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>90</v>
       </c>
       <c r="B235">
-        <v>-54.33070336000002</v>
+        <v>-54.330703360000022</v>
       </c>
       <c r="C235">
-        <v>-22.00429456000001</v>
+        <v>-22.004294560000009</v>
       </c>
       <c r="D235" t="s">
         <v>177</v>
@@ -20353,15 +20431,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="236" spans="1:35">
+    <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>91</v>
       </c>
       <c r="B236">
-        <v>-54.33612882999999</v>
+        <v>-54.336128829999993</v>
       </c>
       <c r="C236">
-        <v>-22.00769850000001</v>
+        <v>-22.007698500000011</v>
       </c>
       <c r="D236" t="s">
         <v>178</v>
@@ -20433,15 +20511,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="237" spans="1:35">
+    <row r="237" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>91</v>
       </c>
       <c r="B237">
-        <v>-54.33612882999999</v>
+        <v>-54.336128829999993</v>
       </c>
       <c r="C237">
-        <v>-22.00769850000001</v>
+        <v>-22.007698500000011</v>
       </c>
       <c r="D237" t="s">
         <v>178</v>
@@ -20510,15 +20588,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="238" spans="1:35">
+    <row r="238" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>92</v>
       </c>
       <c r="B238">
-        <v>-54.33890544</v>
+        <v>-54.338905439999998</v>
       </c>
       <c r="C238">
-        <v>-22.00580730999999</v>
+        <v>-22.005807309999991</v>
       </c>
       <c r="D238" t="s">
         <v>179</v>
@@ -20587,15 +20665,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="239" spans="1:35">
+    <row r="239" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>92</v>
       </c>
       <c r="B239">
-        <v>-54.33890544</v>
+        <v>-54.338905439999998</v>
       </c>
       <c r="C239">
-        <v>-22.00580730999999</v>
+        <v>-22.005807309999991</v>
       </c>
       <c r="D239" t="s">
         <v>179</v>
@@ -20664,15 +20742,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="240" spans="1:35">
+    <row r="240" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>93</v>
       </c>
       <c r="B240">
-        <v>-54.35080697000001</v>
+        <v>-54.350806970000008</v>
       </c>
       <c r="C240">
-        <v>-22.00231737999997</v>
+        <v>-22.002317379999969</v>
       </c>
       <c r="D240" t="s">
         <v>180</v>
@@ -20741,15 +20819,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="241" spans="1:35">
+    <row r="241" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>93</v>
       </c>
       <c r="B241">
-        <v>-54.35080697000001</v>
+        <v>-54.350806970000008</v>
       </c>
       <c r="C241">
-        <v>-22.00231737999997</v>
+        <v>-22.002317379999969</v>
       </c>
       <c r="D241" t="s">
         <v>180</v>
@@ -20818,15 +20896,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="242" spans="1:35">
+    <row r="242" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>94</v>
       </c>
       <c r="B242">
-        <v>-54.34764715999997</v>
+        <v>-54.347647159999973</v>
       </c>
       <c r="C242">
-        <v>-21.99780635999998</v>
+        <v>-21.997806359999981</v>
       </c>
       <c r="D242" t="s">
         <v>181</v>
@@ -20898,15 +20976,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="243" spans="1:35">
+    <row r="243" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>94</v>
       </c>
       <c r="B243">
-        <v>-54.34764715999997</v>
+        <v>-54.347647159999973</v>
       </c>
       <c r="C243">
-        <v>-21.99780635999998</v>
+        <v>-21.997806359999981</v>
       </c>
       <c r="D243" t="s">
         <v>181</v>
@@ -20975,15 +21053,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="244" spans="1:35">
+    <row r="244" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>95</v>
       </c>
       <c r="B244">
-        <v>-54.32855989000002</v>
+        <v>-54.328559890000022</v>
       </c>
       <c r="C244">
-        <v>-22.01022247999999</v>
+        <v>-22.010222479999989</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -21052,15 +21130,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="245" spans="1:35">
+    <row r="245" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>95</v>
       </c>
       <c r="B245">
-        <v>-54.32855989000002</v>
+        <v>-54.328559890000022</v>
       </c>
       <c r="C245">
-        <v>-22.01022247999999</v>
+        <v>-22.010222479999989</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -21129,15 +21207,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="246" spans="1:35">
+    <row r="246" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>96</v>
       </c>
       <c r="B246">
-        <v>-54.32556319000001</v>
+        <v>-54.325563190000011</v>
       </c>
       <c r="C246">
-        <v>-21.99629240000002</v>
+        <v>-21.996292400000019</v>
       </c>
       <c r="D246" t="s">
         <v>183</v>
@@ -21206,15 +21284,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="247" spans="1:35">
+    <row r="247" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>96</v>
       </c>
       <c r="B247">
-        <v>-54.32556319000001</v>
+        <v>-54.325563190000011</v>
       </c>
       <c r="C247">
-        <v>-21.99629240000002</v>
+        <v>-21.996292400000019</v>
       </c>
       <c r="D247" t="s">
         <v>183</v>
@@ -21283,15 +21361,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="248" spans="1:35">
+    <row r="248" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>97</v>
       </c>
       <c r="B248">
-        <v>-54.32292224</v>
+        <v>-54.322922239999997</v>
       </c>
       <c r="C248">
-        <v>-21.9931539</v>
+        <v>-21.993153899999999</v>
       </c>
       <c r="D248" t="s">
         <v>184</v>
@@ -21363,15 +21441,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="249" spans="1:35">
+    <row r="249" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>97</v>
       </c>
       <c r="B249">
-        <v>-54.32292224</v>
+        <v>-54.322922239999997</v>
       </c>
       <c r="C249">
-        <v>-21.9931539</v>
+        <v>-21.993153899999999</v>
       </c>
       <c r="D249" t="s">
         <v>184</v>
@@ -21440,7 +21518,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="250" spans="1:35">
+    <row r="250" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>98</v>
       </c>
@@ -21517,7 +21595,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="251" spans="1:35">
+    <row r="251" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>98</v>
       </c>
@@ -21594,12 +21672,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="252" spans="1:35">
+    <row r="252" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>99</v>
       </c>
       <c r="B252">
-        <v>-54.31467374000002</v>
+        <v>-54.314673740000018</v>
       </c>
       <c r="C252">
         <v>-22.0001316</v>
@@ -21671,12 +21749,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="253" spans="1:35">
+    <row r="253" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>99</v>
       </c>
       <c r="B253">
-        <v>-54.31467374000002</v>
+        <v>-54.314673740000018</v>
       </c>
       <c r="C253">
         <v>-22.0001316</v>
@@ -21748,15 +21826,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="254" spans="1:35">
+    <row r="254" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>100</v>
       </c>
       <c r="B254">
-        <v>-54.31086087999999</v>
+        <v>-54.310860879999993</v>
       </c>
       <c r="C254">
-        <v>-21.99591236999997</v>
+        <v>-21.995912369999971</v>
       </c>
       <c r="D254" t="s">
         <v>187</v>
@@ -21828,15 +21906,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="255" spans="1:35">
+    <row r="255" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>100</v>
       </c>
       <c r="B255">
-        <v>-54.31086087999999</v>
+        <v>-54.310860879999993</v>
       </c>
       <c r="C255">
-        <v>-21.99591236999997</v>
+        <v>-21.995912369999971</v>
       </c>
       <c r="D255" t="s">
         <v>187</v>
@@ -21905,12 +21983,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="256" spans="1:35">
+    <row r="256" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>101</v>
       </c>
       <c r="B256">
-        <v>-54.30489578</v>
+        <v>-54.304895780000003</v>
       </c>
       <c r="C256">
         <v>-21.99905659999996</v>
@@ -21982,12 +22060,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="257" spans="1:35">
+    <row r="257" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>101</v>
       </c>
       <c r="B257">
-        <v>-54.30489578</v>
+        <v>-54.304895780000003</v>
       </c>
       <c r="C257">
         <v>-21.99905659999996</v>
@@ -22059,15 +22137,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="258" spans="1:35">
+    <row r="258" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>102</v>
       </c>
       <c r="B258">
-        <v>-54.30055744999998</v>
+        <v>-54.300557449999978</v>
       </c>
       <c r="C258">
-        <v>-22.00170467999997</v>
+        <v>-22.001704679999971</v>
       </c>
       <c r="D258" t="s">
         <v>189</v>
@@ -22139,15 +22217,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="259" spans="1:35">
+    <row r="259" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>102</v>
       </c>
       <c r="B259">
-        <v>-54.30055744999998</v>
+        <v>-54.300557449999978</v>
       </c>
       <c r="C259">
-        <v>-22.00170467999997</v>
+        <v>-22.001704679999971</v>
       </c>
       <c r="D259" t="s">
         <v>189</v>
@@ -22216,15 +22294,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="260" spans="1:35">
+    <row r="260" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>103</v>
       </c>
       <c r="B260">
-        <v>-54.35592368801336</v>
+        <v>-54.355923688013362</v>
       </c>
       <c r="C260">
-        <v>-22.0029021674815</v>
+        <v>-22.002902167481501</v>
       </c>
       <c r="D260" t="s">
         <v>190</v>
@@ -22293,15 +22371,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="261" spans="1:35">
+    <row r="261" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>103</v>
       </c>
       <c r="B261">
-        <v>-54.35592368801336</v>
+        <v>-54.355923688013362</v>
       </c>
       <c r="C261">
-        <v>-22.0029021674815</v>
+        <v>-22.002902167481501</v>
       </c>
       <c r="D261" t="s">
         <v>190</v>
@@ -22370,15 +22448,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="262" spans="1:35">
+    <row r="262" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>104</v>
       </c>
       <c r="B262">
-        <v>-54.25679754000002</v>
+        <v>-54.256797540000022</v>
       </c>
       <c r="C262">
-        <v>-22.03801285999998</v>
+        <v>-22.038012859999981</v>
       </c>
       <c r="D262" t="s">
         <v>191</v>
@@ -22450,15 +22528,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="263" spans="1:35">
+    <row r="263" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>104</v>
       </c>
       <c r="B263">
-        <v>-54.25679754000002</v>
+        <v>-54.256797540000022</v>
       </c>
       <c r="C263">
-        <v>-22.03801285999998</v>
+        <v>-22.038012859999981</v>
       </c>
       <c r="D263" t="s">
         <v>191</v>
@@ -22527,12 +22605,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="264" spans="1:35">
+    <row r="264" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>105</v>
       </c>
       <c r="B264">
-        <v>-54.25560439999998</v>
+        <v>-54.255604399999982</v>
       </c>
       <c r="C264">
         <v>-22.02982373999998</v>
@@ -22604,12 +22682,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="265" spans="1:35">
+    <row r="265" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>105</v>
       </c>
       <c r="B265">
-        <v>-54.25560439999998</v>
+        <v>-54.255604399999982</v>
       </c>
       <c r="C265">
         <v>-22.02982373999998</v>
@@ -22681,15 +22759,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="266" spans="1:35">
+    <row r="266" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>106</v>
       </c>
       <c r="B266">
-        <v>-54.25079804</v>
+        <v>-54.250798039999999</v>
       </c>
       <c r="C266">
-        <v>-22.03855477999999</v>
+        <v>-22.038554779999991</v>
       </c>
       <c r="D266" t="s">
         <v>193</v>
@@ -22758,15 +22836,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="267" spans="1:35">
+    <row r="267" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>106</v>
       </c>
       <c r="B267">
-        <v>-54.25079804</v>
+        <v>-54.250798039999999</v>
       </c>
       <c r="C267">
-        <v>-22.03855477999999</v>
+        <v>-22.038554779999991</v>
       </c>
       <c r="D267" t="s">
         <v>193</v>
@@ -22835,12 +22913,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="268" spans="1:35">
+    <row r="268" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>107</v>
       </c>
       <c r="B268">
-        <v>-54.24920092000002</v>
+        <v>-54.249200920000021</v>
       </c>
       <c r="C268">
         <v>-22.03116389999996</v>
@@ -22912,12 +22990,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="269" spans="1:35">
+    <row r="269" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>107</v>
       </c>
       <c r="B269">
-        <v>-54.24920092000002</v>
+        <v>-54.249200920000021</v>
       </c>
       <c r="C269">
         <v>-22.03116389999996</v>
@@ -22989,12 +23067,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="270" spans="1:35">
+    <row r="270" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>108</v>
       </c>
       <c r="B270">
-        <v>-54.24518842999996</v>
+        <v>-54.245188429999963</v>
       </c>
       <c r="C270">
         <v>-22.0264764</v>
@@ -23069,12 +23147,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="271" spans="1:35">
+    <row r="271" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>108</v>
       </c>
       <c r="B271">
-        <v>-54.24518842999996</v>
+        <v>-54.245188429999963</v>
       </c>
       <c r="C271">
         <v>-22.0264764</v>
@@ -23146,7 +23224,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="272" spans="1:35">
+    <row r="272" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>109</v>
       </c>
@@ -23154,7 +23232,7 @@
         <v>-54.24435548000001</v>
       </c>
       <c r="C272">
-        <v>-22.03651415</v>
+        <v>-22.036514149999999</v>
       </c>
       <c r="D272" t="s">
         <v>196</v>
@@ -23226,7 +23304,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="273" spans="1:35">
+    <row r="273" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>109</v>
       </c>
@@ -23234,7 +23312,7 @@
         <v>-54.24435548000001</v>
       </c>
       <c r="C273">
-        <v>-22.03651415</v>
+        <v>-22.036514149999999</v>
       </c>
       <c r="D273" t="s">
         <v>196</v>
@@ -23303,15 +23381,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="274" spans="1:35">
+    <row r="274" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>110</v>
       </c>
       <c r="B274">
-        <v>-54.24054463999998</v>
+        <v>-54.240544639999982</v>
       </c>
       <c r="C274">
-        <v>-22.03453082</v>
+        <v>-22.034530820000001</v>
       </c>
       <c r="D274" t="s">
         <v>197</v>
@@ -23380,15 +23458,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="275" spans="1:35">
+    <row r="275" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>110</v>
       </c>
       <c r="B275">
-        <v>-54.24054463999998</v>
+        <v>-54.240544639999982</v>
       </c>
       <c r="C275">
-        <v>-22.03453082</v>
+        <v>-22.034530820000001</v>
       </c>
       <c r="D275" t="s">
         <v>197</v>
@@ -23457,15 +23535,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="276" spans="1:35">
+    <row r="276" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>111</v>
       </c>
       <c r="B276">
-        <v>-54.23389304999999</v>
+        <v>-54.233893049999992</v>
       </c>
       <c r="C276">
-        <v>-22.03821104000001</v>
+        <v>-22.038211040000011</v>
       </c>
       <c r="D276" t="s">
         <v>198</v>
@@ -23537,15 +23615,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="277" spans="1:35">
+    <row r="277" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>111</v>
       </c>
       <c r="B277">
-        <v>-54.23389304999999</v>
+        <v>-54.233893049999992</v>
       </c>
       <c r="C277">
-        <v>-22.03821104000001</v>
+        <v>-22.038211040000011</v>
       </c>
       <c r="D277" t="s">
         <v>198</v>
@@ -23614,15 +23692,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="278" spans="1:35">
+    <row r="278" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>112</v>
       </c>
       <c r="B278">
-        <v>-54.23375242000001</v>
+        <v>-54.233752420000009</v>
       </c>
       <c r="C278">
-        <v>-22.03357473999999</v>
+        <v>-22.033574739999992</v>
       </c>
       <c r="D278" t="s">
         <v>199</v>
@@ -23691,15 +23769,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="279" spans="1:35">
+    <row r="279" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>112</v>
       </c>
       <c r="B279">
-        <v>-54.23375242000001</v>
+        <v>-54.233752420000009</v>
       </c>
       <c r="C279">
-        <v>-22.03357473999999</v>
+        <v>-22.033574739999992</v>
       </c>
       <c r="D279" t="s">
         <v>199</v>
@@ -23768,7 +23846,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="280" spans="1:35">
+    <row r="280" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>113</v>
       </c>
@@ -23776,7 +23854,7 @@
         <v>-54.23569915999996</v>
       </c>
       <c r="C280">
-        <v>-22.03089171</v>
+        <v>-22.030891709999999</v>
       </c>
       <c r="D280" t="s">
         <v>200</v>
@@ -23845,7 +23923,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="281" spans="1:35">
+    <row r="281" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>113</v>
       </c>
@@ -23853,7 +23931,7 @@
         <v>-54.23569915999996</v>
       </c>
       <c r="C281">
-        <v>-22.03089171</v>
+        <v>-22.030891709999999</v>
       </c>
       <c r="D281" t="s">
         <v>200</v>
@@ -23922,12 +24000,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="282" spans="1:35">
+    <row r="282" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>114</v>
       </c>
       <c r="B282">
-        <v>-54.23571390000001</v>
+        <v>-54.235713900000007</v>
       </c>
       <c r="C282">
         <v>-22.02727519999997</v>
@@ -23999,12 +24077,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="283" spans="1:35">
+    <row r="283" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>114</v>
       </c>
       <c r="B283">
-        <v>-54.23571390000001</v>
+        <v>-54.235713900000007</v>
       </c>
       <c r="C283">
         <v>-22.02727519999997</v>
@@ -24076,15 +24154,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="284" spans="1:35">
+    <row r="284" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>115</v>
       </c>
       <c r="B284">
-        <v>-54.23793315</v>
+        <v>-54.237933150000003</v>
       </c>
       <c r="C284">
-        <v>-22.02081752999999</v>
+        <v>-22.020817529999992</v>
       </c>
       <c r="D284" t="s">
         <v>202</v>
@@ -24156,15 +24234,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="285" spans="1:35">
+    <row r="285" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>115</v>
       </c>
       <c r="B285">
-        <v>-54.23793315</v>
+        <v>-54.237933150000003</v>
       </c>
       <c r="C285">
-        <v>-22.02081752999999</v>
+        <v>-22.020817529999992</v>
       </c>
       <c r="D285" t="s">
         <v>202</v>
@@ -24233,15 +24311,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="286" spans="1:35">
+    <row r="286" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>116</v>
       </c>
       <c r="B286">
-        <v>-54.23189519</v>
+        <v>-54.231895190000003</v>
       </c>
       <c r="C286">
-        <v>-22.02223451999999</v>
+        <v>-22.022234519999991</v>
       </c>
       <c r="D286" t="s">
         <v>203</v>
@@ -24310,15 +24388,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="287" spans="1:35">
+    <row r="287" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>116</v>
       </c>
       <c r="B287">
-        <v>-54.23189519</v>
+        <v>-54.231895190000003</v>
       </c>
       <c r="C287">
-        <v>-22.02223451999999</v>
+        <v>-22.022234519999991</v>
       </c>
       <c r="D287" t="s">
         <v>203</v>
@@ -24387,15 +24465,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="288" spans="1:35">
+    <row r="288" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>117</v>
       </c>
       <c r="B288">
-        <v>-54.22735566999999</v>
+        <v>-54.227355669999987</v>
       </c>
       <c r="C288">
-        <v>-22.02651201000001</v>
+        <v>-22.026512010000008</v>
       </c>
       <c r="D288" t="s">
         <v>204</v>
@@ -24467,15 +24545,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="289" spans="1:35">
+    <row r="289" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>117</v>
       </c>
       <c r="B289">
-        <v>-54.22735566999999</v>
+        <v>-54.227355669999987</v>
       </c>
       <c r="C289">
-        <v>-22.02651201000001</v>
+        <v>-22.026512010000008</v>
       </c>
       <c r="D289" t="s">
         <v>204</v>
@@ -24544,12 +24622,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="290" spans="1:35">
+    <row r="290" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>118</v>
       </c>
       <c r="B290">
-        <v>-54.23021097999998</v>
+        <v>-54.230210979999981</v>
       </c>
       <c r="C290">
         <v>-22.02780948000002</v>
@@ -24621,12 +24699,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="291" spans="1:35">
+    <row r="291" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>118</v>
       </c>
       <c r="B291">
-        <v>-54.23021097999998</v>
+        <v>-54.230210979999981</v>
       </c>
       <c r="C291">
         <v>-22.02780948000002</v>
@@ -24698,12 +24776,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="292" spans="1:35">
+    <row r="292" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>119</v>
       </c>
       <c r="B292">
-        <v>-54.22638590999999</v>
+        <v>-54.226385909999991</v>
       </c>
       <c r="C292">
         <v>-22.02023538000001</v>
@@ -24775,12 +24853,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="293" spans="1:35">
+    <row r="293" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>119</v>
       </c>
       <c r="B293">
-        <v>-54.22638590999999</v>
+        <v>-54.226385909999991</v>
       </c>
       <c r="C293">
         <v>-22.02023538000001</v>
@@ -24852,15 +24930,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="294" spans="1:35">
+    <row r="294" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>120</v>
       </c>
       <c r="B294">
-        <v>-54.21944063999997</v>
+        <v>-54.219440639999974</v>
       </c>
       <c r="C294">
-        <v>-22.01660104000001</v>
+        <v>-22.016601040000008</v>
       </c>
       <c r="D294" t="s">
         <v>207</v>
@@ -24932,15 +25010,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="295" spans="1:35">
+    <row r="295" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>120</v>
       </c>
       <c r="B295">
-        <v>-54.21944063999997</v>
+        <v>-54.219440639999974</v>
       </c>
       <c r="C295">
-        <v>-22.01660104000001</v>
+        <v>-22.016601040000008</v>
       </c>
       <c r="D295" t="s">
         <v>207</v>
@@ -25009,7 +25087,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="296" spans="1:35">
+    <row r="296" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>121</v>
       </c>
@@ -25017,7 +25095,7 @@
         <v>-54.21922302527593</v>
       </c>
       <c r="C296">
-        <v>-22.09451063011043</v>
+        <v>-22.094510630110431</v>
       </c>
       <c r="D296" t="s">
         <v>208</v>
@@ -25089,7 +25167,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="297" spans="1:35">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>121</v>
       </c>
@@ -25097,7 +25175,7 @@
         <v>-54.21922302527593</v>
       </c>
       <c r="C297">
-        <v>-22.09451063011043</v>
+        <v>-22.094510630110431</v>
       </c>
       <c r="D297" t="s">
         <v>208</v>
